--- a/courses/3/is-testing/dist/Учебный_план_Тестирование_информационных_систем.xlsx
+++ b/courses/3/is-testing/dist/Учебный_план_Тестирование_информационных_систем.xlsx
@@ -174,7 +174,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
@@ -195,16 +195,16 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Тестирование ИС»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Тестирование проверяет, что система делает нужное и не ломается на неожиданных данных. Разбираются цели проверок, цена дефекта и место тестов в жизненном цикле ИС.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестирование ИС</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
+          <t xml:space="preserve">качество ПО, дефект, верификация, валидация, стоимость дефекта</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
@@ -225,16 +225,16 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Виды тестирования»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Виды тестирования различаются по объекту, этапу, доступу к коду и степени автоматизации. Классификация помогает выбрать проверки под конкретный риск.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Виды тестирования</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t xml:space="preserve">функциональное тестирование, нефункциональное тестирование, чёрный ящик, белый ящик, дымовое тестирование, регрессия</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">3-4</t>
@@ -255,12 +255,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Тест-план; Классы эквивалентности.</t>
+          <t xml:space="preserve">Студенты составляют тест-план учебной ИС и разбивают поля ввода на классы эквивалентности. Сдают тест-план и таблицу классов с обоснованием выбранных значений.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тест-план, Классы эквивалентности</t>
+          <t xml:space="preserve">область значений, представитель класса, критерии выхода, объём проверок, риск</t>
         </is>
       </c>
     </row>
@@ -285,16 +285,16 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Тест-дизайн»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Тест-дизайн отвечает, какие проверки дадут максимум информации при минимуме тестов. Разбираются техники проектирования и выбор между ними.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тест-дизайн</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1">
+          <t xml:space="preserve">техника, покрытие, тестовые данные, оракул, эвристика</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
@@ -315,16 +315,16 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Классы эквивалентности»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Область значений поля делится на классы, внутри которых поведение системы одинаково. Один тест на класс заменяет перебор всех допустимых значений.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Классы эквивалентности</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+          <t xml:space="preserve">разбиение области, корректный класс, некорректный класс, представитель класса, тестовые данные</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">7-8</t>
@@ -345,16 +345,16 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Граничные значения; Тест-кейсы.</t>
+          <t xml:space="preserve">Студенты проверяют форму ввода граничными значениями и оформляют найденные проверки как тест-кейсы. Сдают набор тест-кейсов с шагами, данными и ожидаемым результатом.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Граничные значения, Тест-кейсы</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
+          <t xml:space="preserve">шаг теста, ожидаемый результат, тестовые данные, предусловие, воспроизводимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
@@ -375,16 +375,16 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Граничные значения»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Ошибки чаще всего прячутся на границах диапазона и в точках смены поведения. Разбирается анализ граничных значений и его сочетание с классами эквивалентности.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Граничные значения</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t xml:space="preserve">граница, диапазон, точка перехода, вне диапазона, крайнее значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
@@ -405,16 +405,16 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Тест-кейсы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Тест-кейс фиксирует предусловие, шаги, данные и ожидаемый результат так, чтобы проверку повторил другой человек. Разбирается структура и уровень детализации.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тест-кейсы</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+          <t xml:space="preserve">предусловие, шаг, ожидаемый результат, постусловие, приоритет, шаблон</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">11-12</t>
@@ -435,16 +435,16 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Чек-лист; Тестирование требований.</t>
+          <t xml:space="preserve">Студенты проверяют требования учебной ИС по чек-листу и фиксируют противоречия, пробелы и непроверяемые формулировки. Сдают чек-лист и список замечаний с вопросами к заказчику.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чек-лист, Тестирование требований</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
+          <t xml:space="preserve">требование, неоднозначность, пробел, трассируемость, вопрос к заказчику</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
@@ -465,12 +465,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Чек-листы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Чек-лист задаёт список проверок без шагов и ожидаемых результатов. Разбирается, когда чек-лист дешевле тест-кейса и как поддерживать его вместе с требованиями.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чек-листы</t>
+          <t xml:space="preserve">пункт проверки, покрытие, регресс, шаблон, поддержка</t>
         </is>
       </c>
     </row>
@@ -495,16 +495,16 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Тестирование требований»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Дефект в требовании дешевле найти до появления кода. Разбирается, как проверять полноту, непротиворечивость и проверяемость требований к системе.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестирование требований</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
+          <t xml:space="preserve">требование, полнота, противоречие, проверяемость, трассируемость, критерий приёмки</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">15-16</t>
@@ -525,16 +525,16 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Функциональные тесты; Интеграционные тесты.</t>
+          <t xml:space="preserve">Студенты проверяют функции учебной ИС по требованиям и стыки между модулями. Сдают набор функциональных и интеграционных тестов с результатами прогона.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Функциональные тесты, Интеграционные тесты</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
+          <t xml:space="preserve">стык модулей, тестовый стенд, протокол прогона, сценарий, покрытие</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
@@ -555,16 +555,16 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Функциональное тестирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Функциональные тесты проверяют, что система делает записанное в требованиях. Разбираются покрытие функций, подготовка данных и работа с ожидаемым результатом.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Функциональное тестирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
+          <t xml:space="preserve">функция, ожидаемый результат, покрытие, сценарий, требование</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
@@ -585,16 +585,16 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Системные тесты»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты проверяют учебную ИС целиком на соответствие сценариям пользователя. Сдают протокол системного прогона с найденными дефектами и оценкой готовности.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Системные тесты</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
+          <t xml:space="preserve">сквозной сценарий, окружение, протокол, дефект, пользовательский путь</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
@@ -615,12 +615,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Интеграционное тестирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Интеграционные тесты проверяют, как модули обмениваются данными и кто отвечает за сбой на стыке. Разбираются подходы снизу вверх, сверху вниз и большой скачок.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Интеграционное тестирование</t>
+          <t xml:space="preserve">стык, заглушка, драйвер, снизу вверх, большой скачок, контракт</t>
         </is>
       </c>
     </row>
@@ -645,16 +645,16 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Регрессия»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты подбирают проверки, которые ловят поломки после изменения кода, и прогоняют их по учебной ИС. Сдают регрессионный набор и отчёт о прогоне.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Регрессия</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
+          <t xml:space="preserve">регрессионный набор, зона риска, изменение, прогон, дымовой тест</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">21</t>
@@ -675,16 +675,16 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Системное тестирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Системный тест проверяет готовую ИС в среде, близкой к рабочей: сценарии, данные, окружение и внешние системы. Разбирается, что именно проверяется на этом уровне.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Системное тестирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
+          <t xml:space="preserve">сквозной сценарий, окружение, внешняя система, приёмочный тест, готовность</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
@@ -705,16 +705,16 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Регрессионное тестирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Любое изменение может сломать то, что уже работало. Разбирается, как выбрать регрессионный набор, когда его прогонять и как не утонуть в бесконечных проверках.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Регрессионное тестирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
+          <t xml:space="preserve">набор проверок, риск, автоматизация, дымовой прогон, частота</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">23-24</t>
@@ -735,16 +735,16 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: API-тесты; Postman: коллекция.</t>
+          <t xml:space="preserve">Студенты проверяют методы API учебной ИС в Postman и собирают запросы в коллекцию с переменными окружения. Сдают коллекцию и отчёт о проверке ответов.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">API-тесты, Postman: коллекция</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
+          <t xml:space="preserve">запрос, ответ, переменная окружения, JSON, код состояния</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">25</t>
@@ -765,12 +765,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Тестирование API»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">API проверяют без интерфейса: запрос, ответ, код состояния и тело. Разбираются контракт, негативные проверки и типовые дефекты обмена между системами.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестирование API</t>
+          <t xml:space="preserve">эндпоинт, код состояния, контракт, тело ответа, негативный тест, аутентификация</t>
         </is>
       </c>
     </row>
@@ -795,16 +795,16 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Postman: тесты 200/500/JSON»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты пишут в Postman проверки кода ответа и схемы JSON, включая обработку ошибки 500. Сдают коллекцию с тестами и отчёт о прогоне.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postman: тесты 200/500/JSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
+          <t xml:space="preserve">код ответа, схема JSON, тест-скрипт, прогон коллекции, ошибка сервера</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">27</t>
@@ -825,16 +825,16 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Postman»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Postman хранит запросы, окружения и тесты в одном месте. Разбираются коллекции, переменные, окружения и запуск прогона из интерфейса.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postman</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
+          <t xml:space="preserve">коллекция, папка, переменная, окружение, прогон, тест-скрипт</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">28</t>
@@ -855,12 +855,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Автотесты»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты переводят ручные проверки в автотесты на Python и запускают их на учебной ИС. Сдают набор тестов, который проходит на исправной сборке и падает на дефектной.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Автотесты</t>
+          <t xml:space="preserve">pytest, фикстура, утверждение, отчёт, запуск</t>
         </is>
       </c>
     </row>
@@ -885,16 +885,16 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Автотесты»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Автотест окупается там, где проверку нужно повторять много раз. Разбираются пирамида тестов, выбор уровня автоматизации и цена поддержки набора.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Автотесты</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
+          <t xml:space="preserve">пирамида тестов, модульный тест, UI-тест, фикстура, поддержка, окупаемость</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
@@ -915,16 +915,16 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Нагрузочное тестирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Нагрузочный тест отвечает, как система ведёт себя при росте числа пользователей. Разбираются профиль нагрузки, узкие места и метрики времени отклика.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нагрузочное тестирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
+          <t xml:space="preserve">профиль нагрузки, время отклика, пропускная способность, узкое место, стресс-тест, виртуальный пользователь</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">31-32</t>
@@ -945,16 +945,16 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Нагрузка; Безопасность.</t>
+          <t xml:space="preserve">Студенты задают нагрузку на учебную ИС и проверяют базовые риски безопасности: права доступа, ввод и хранение секретов. Сдают отчёт с метриками и найденными проблемами.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Нагрузка, Безопасность</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
+          <t xml:space="preserve">нагрузочный прогон, метрика, права доступа, валидация ввода, секрет</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">33</t>
@@ -975,16 +975,16 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Безопасность»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Проверки безопасности ищут, где система доверяет пользователю лишнее. Разбираются права доступа, валидация ввода, хранение секретов и типовые атаки на ИС.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Безопасность</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
+          <t xml:space="preserve">доступ, роль, валидация, инъекция, секрет, аутентификация</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">34</t>
@@ -1005,16 +1005,16 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Юзабилити»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты проходят сценарии в интерфейсе учебной ИС и фиксируют затруднения пользователя. Сдают отчёт с найденными проблемами и предложениями по исправлению.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Юзабилити</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+          <t xml:space="preserve">сценарий, эвристика, экран, затруднение, отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">35</t>
@@ -1035,16 +1035,16 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Юзабилити»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Удобство оценивают по тому, как быстро и без ошибок пользователь решает свою задачу. Разбираются эвристики, сценарии проверки и метрики удобства интерфейса.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Юзабилити</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
+          <t xml:space="preserve">эвристика, сценарий, метрика, обратная связь, доступность, экран</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">36</t>
@@ -1065,16 +1065,16 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Дефекты и баг-трекинг»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Дефект проходит путь от обнаружения до закрытия, и на каждом шаге у него свой владелец. Разбираются жизненный цикл, серьёзность и приоритет исправления.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дефекты и баг-трекинг</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
+          <t xml:space="preserve">статус, серьёзность, приоритет, жизненный цикл, исправление, трекер</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">37-38</t>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Баг-репорт; Bug tracking.</t>
+          <t xml:space="preserve">Студенты воспроизводят дефекты учебной ИС, оформляют баг-репорты и проводят их по статусам в трекере. Сдают набор баг-репортов и выгрузку истории статусов.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Баг-репорт, Bug tracking</t>
+          <t xml:space="preserve">шаги воспроизведения, трекер, статус, исправление, серьёзность, окружение</t>
         </is>
       </c>
     </row>
@@ -1125,16 +1125,16 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Отчётность»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Отчёт о тестировании показывает, что проверено, что найдено и можно ли выпускать систему. Разбираются метрики, структура отчёта и вывод по качеству.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отчётность</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="45" customHeight="1">
+          <t xml:space="preserve">метрика, покрытие, готовность, динамика дефектов, вывод, структура</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">40</t>
@@ -1155,16 +1155,16 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Организация тестирования»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Тестирование встраивается в работу команды: роли, уровни, вход и выход из этапов. Разбираются стратегия, оценка трудозатрат и работа с рисками качества.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Организация тестирования</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
+          <t xml:space="preserve">стратегия, роль, оценка, риск, процесс, метрика</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">41-42</t>
@@ -1185,16 +1185,16 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Отчёт; Тестовая документация.</t>
+          <t xml:space="preserve">Студенты собирают пакет тестовой документации по учебной ИС: план, наборы, отчёт и матрицу покрытия. Сдают документы, согласованные между собой.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Отчёт, Тестовая документация</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
+          <t xml:space="preserve">матрица покрытия, шаблон, версия, согласованность, пакет документов</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">43-44</t>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Тестирование БД; Тестирование интерфейса.</t>
+          <t xml:space="preserve">Студенты проверяют сохранение данных в БД и работу интерфейса учебной ИС. Сдают SQL-запросы проверки данных и набор тестов интерфейса с результатами.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестирование БД, Тестирование интерфейса</t>
+          <t xml:space="preserve">целостность данных, SQL-проверка, валидация поля, расхождение, транзакция</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Тестирование интеграций»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты проверяют обмен учебной ИС с внешним сервисом и поведение при сбое. Сдают набор тестов интеграции и отчёт об обработке ошибок.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестирование интеграций</t>
+          <t xml:space="preserve">внешний сервис, таймаут, повтор, идемпотентность, очередь</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Мини-проект»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты проводят цикл тестирования небольшой ИС от плана до отчёта. Сдают пакет документов и защищают принятые решения по объёму проверок.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мини-проект</t>
+          <t xml:space="preserve">цикл тестирования, план, дефект, отчёт, защита</t>
         </is>
       </c>
     </row>
@@ -1305,16 +1305,16 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Итоговый отчёт»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты сводят результаты проверок в итоговый отчёт с метриками и выводом о готовности. Сдают отчёт и презентацию для защиты.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итоговый отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="45" customHeight="1">
+          <t xml:space="preserve">метрика, готовность, презентация, вывод, сводка</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">48</t>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Защита»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Студенты защищают результаты тестирования учебной ИС: объём проверок, найденные дефекты и вывод о качестве. Сдают доклад и отвечают на вопросы по решениям.</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита</t>
+          <t xml:space="preserve">доклад, обоснование, вопросы, качество, вывод</t>
         </is>
       </c>
     </row>

--- a/courses/3/is-testing/dist/Учебный_план_Тестирование_информационных_систем.xlsx
+++ b/courses/3/is-testing/dist/Учебный_план_Тестирование_информационных_систем.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D33" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D34" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D35" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D36" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D37" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D38" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="D39" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="D40" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D41" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="D42" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="D43" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D44" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="D45" s="6">
-        <v>4320</v>
+        <v>96</v>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>

--- a/courses/3/is-testing/dist/Учебный_план_Тестирование_информационных_систем.xlsx
+++ b/courses/3/is-testing/dist/Учебный_план_Тестирование_информационных_систем.xlsx
@@ -234,40 +234,40 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3-4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Тест-план; Классы эквивалентности</t>
+          <t xml:space="preserve">Лекция 3. Тест-дизайн</t>
         </is>
       </c>
       <c r="D8" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты составляют тест-план учебной ИС и разбивают поля ввода на классы эквивалентности. Сдают тест-план и таблицу классов с обоснованием выбранных значений.</t>
+          <t xml:space="preserve">Тест-дизайн отвечает, какие проверки дадут максимум информации при минимуме тестов. Разбираются техники проектирования и выбор между ними.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">область значений, представитель класса, критерии выхода, объём проверок, риск</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
+          <t xml:space="preserve">техника, покрытие, тестовые данные, оракул, эвристика</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -277,7 +277,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 3. Тест-дизайн</t>
+          <t xml:space="preserve">Лекция 4. Классы эквивалентности</t>
         </is>
       </c>
       <c r="D9" s="6">
@@ -285,79 +285,79 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тест-дизайн отвечает, какие проверки дадут максимум информации при минимуме тестов. Разбираются техники проектирования и выбор между ними.</t>
+          <t xml:space="preserve">Область значений поля делится на классы, внутри которых поведение системы одинаково. Один тест на класс заменяет перебор всех допустимых значений.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">техника, покрытие, тестовые данные, оракул, эвристика</t>
+          <t xml:space="preserve">разбиение области, корректный класс, некорректный класс, представитель класса, тестовые данные</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5-6</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 4. Классы эквивалентности</t>
+          <t xml:space="preserve">Практика 1. Тест-план; Классы эквивалентности</t>
         </is>
       </c>
       <c r="D10" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Область значений поля делится на классы, внутри которых поведение системы одинаково. Один тест на класс заменяет перебор всех допустимых значений.</t>
+          <t xml:space="preserve">Студенты составляют тест-план учебной ИС и разбивают поля ввода на классы эквивалентности. Сдают тест-план и таблицу классов с обоснованием выбранных значений.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">разбиение области, корректный класс, некорректный класс, представитель класса, тестовые данные</t>
+          <t xml:space="preserve">область значений, представитель класса, критерии выхода, объём проверок, риск</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7-8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 2. Граничные значения; Тест-кейсы</t>
+          <t xml:space="preserve">Лекция 5. Граничные значения</t>
         </is>
       </c>
       <c r="D11" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проверяют форму ввода граничными значениями и оформляют найденные проверки как тест-кейсы. Сдают набор тест-кейсов с шагами, данными и ожидаемым результатом.</t>
+          <t xml:space="preserve">Ошибки чаще всего прячутся на границах диапазона и в точках смены поведения. Разбирается анализ граничных значений и его сочетание с классами эквивалентности.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">шаг теста, ожидаемый результат, тестовые данные, предусловие, воспроизводимость</t>
+          <t xml:space="preserve">граница, диапазон, точка перехода, вне диапазона, крайнее значение</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -367,7 +367,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 5. Граничные значения</t>
+          <t xml:space="preserve">Лекция 6. Тест-кейсы</t>
         </is>
       </c>
       <c r="D12" s="6">
@@ -375,169 +375,169 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ошибки чаще всего прячутся на границах диапазона и в точках смены поведения. Разбирается анализ граничных значений и его сочетание с классами эквивалентности.</t>
+          <t xml:space="preserve">Тест-кейс фиксирует предусловие, шаги, данные и ожидаемый результат так, чтобы проверку повторил другой человек. Разбирается структура и уровень детализации.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">граница, диапазон, точка перехода, вне диапазона, крайнее значение</t>
+          <t xml:space="preserve">предусловие, шаг, ожидаемый результат, постусловие, приоритет, шаблон</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9-10</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 6. Тест-кейсы</t>
+          <t xml:space="preserve">Практика 2. Граничные значения; Тест-кейсы</t>
         </is>
       </c>
       <c r="D13" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тест-кейс фиксирует предусловие, шаги, данные и ожидаемый результат так, чтобы проверку повторил другой человек. Разбирается структура и уровень детализации.</t>
+          <t xml:space="preserve">Студенты проверяют форму ввода граничными значениями и оформляют найденные проверки как тест-кейсы. Сдают набор тест-кейсов с шагами, данными и ожидаемым результатом.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">предусловие, шаг, ожидаемый результат, постусловие, приоритет, шаблон</t>
+          <t xml:space="preserve">шаг теста, ожидаемый результат, тестовые данные, предусловие, воспроизводимость</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11-12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Лекция 7. Чек-листы</t>
+        </is>
+      </c>
+      <c r="D14" s="6">
+        <v>2</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чек-лист задаёт список проверок без шагов и ожидаемых результатов. Разбирается, когда чек-лист дешевле тест-кейса и как поддерживать его вместе с требованиями.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">пункт проверки, покрытие, регресс, шаблон, поддержка</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 8. Тестирование требований</t>
+        </is>
+      </c>
+      <c r="D15" s="6">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дефект в требовании дешевле найти до появления кода. Разбирается, как проверять полноту, непротиворечивость и проверяемость требований к системе.</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">требование, полнота, противоречие, проверяемость, трассируемость, критерий приёмки</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13-14</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика 3. Чек-лист; Тестирование требований</t>
         </is>
       </c>
-      <c r="D14" s="6">
+      <c r="D16" s="6">
         <v>4</v>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Студенты проверяют требования учебной ИС по чек-листу и фиксируют противоречия, пробелы и непроверяемые формулировки. Сдают чек-лист и список замечаний с вопросами к заказчику.</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">требование, неоднозначность, пробел, трассируемость, вопрос к заказчику</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 7. Чек-листы</t>
-        </is>
-      </c>
-      <c r="D15" s="6">
-        <v>2</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Чек-лист задаёт список проверок без шагов и ожидаемых результатов. Разбирается, когда чек-лист дешевле тест-кейса и как поддерживать его вместе с требованиями.</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">пункт проверки, покрытие, регресс, шаблон, поддержка</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 8. Тестирование требований</t>
-        </is>
-      </c>
-      <c r="D16" s="6">
-        <v>2</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Дефект в требовании дешевле найти до появления кода. Разбирается, как проверять полноту, непротиворечивость и проверяемость требований к системе.</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">требование, полнота, противоречие, проверяемость, трассируемость, критерий приёмки</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">15-16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 4. Функциональные тесты; Интеграционные тесты</t>
+          <t xml:space="preserve">Лекция 9. Функциональное тестирование</t>
         </is>
       </c>
       <c r="D17" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проверяют функции учебной ИС по требованиям и стыки между модулями. Сдают набор функциональных и интеграционных тестов с результатами прогона.</t>
+          <t xml:space="preserve">Функциональные тесты проверяют, что система делает записанное в требованиях. Разбираются покрытие функций, подготовка данных и работа с ожидаемым результатом.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">стык модулей, тестовый стенд, протокол прогона, сценарий, покрытие</t>
+          <t xml:space="preserve">функция, ожидаемый результат, покрытие, сценарий, требование</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 9. Функциональное тестирование</t>
+          <t xml:space="preserve">Лекция 10. Интеграционное тестирование</t>
         </is>
       </c>
       <c r="D18" s="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Функциональные тесты проверяют, что система делает записанное в требованиях. Разбираются покрытие функций, подготовка данных и работа с ожидаемым результатом.</t>
+          <t xml:space="preserve">Интеграционные тесты проверяют, как модули обмениваются данными и кто отвечает за сбой на стыке. Разбираются подходы снизу вверх, сверху вниз и большой скачок.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">функция, ожидаемый результат, покрытие, сценарий, требование</t>
+          <t xml:space="preserve">стык, заглушка, драйвер, снизу вверх, большой скачок, контракт</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">17-18</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -577,20 +577,20 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. Системные тесты</t>
+          <t xml:space="preserve">Практика 4. Функциональные тесты; Интеграционные тесты</t>
         </is>
       </c>
       <c r="D19" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проверяют учебную ИС целиком на соответствие сценариям пользователя. Сдают протокол системного прогона с найденными дефектами и оценкой готовности.</t>
+          <t xml:space="preserve">Студенты проверяют функции учебной ИС по требованиям и стыки между модулями. Сдают набор функциональных и интеграционных тестов с результатами прогона.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">сквозной сценарий, окружение, протокол, дефект, пользовательский путь</t>
+          <t xml:space="preserve">стык модулей, тестовый стенд, протокол прогона, сценарий, покрытие</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 10. Интеграционное тестирование</t>
+          <t xml:space="preserve">Лекция 11. Системное тестирование</t>
         </is>
       </c>
       <c r="D20" s="6">
@@ -615,16 +615,16 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Интеграционные тесты проверяют, как модули обмениваются данными и кто отвечает за сбой на стыке. Разбираются подходы снизу вверх, сверху вниз и большой скачок.</t>
+          <t xml:space="preserve">Системный тест проверяет готовую ИС в среде, близкой к рабочей: сценарии, данные, окружение и внешние системы. Разбирается, что именно проверяется на этом уровне.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">стык, заглушка, драйвер, снизу вверх, большой скачок, контракт</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+          <t xml:space="preserve">сквозной сценарий, окружение, внешняя система, приёмочный тест, готовность</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
@@ -637,7 +637,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 6. Регрессия</t>
+          <t xml:space="preserve">Практика 5. Системные тесты</t>
         </is>
       </c>
       <c r="D21" s="6">
@@ -645,12 +645,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты подбирают проверки, которые ловят поломки после изменения кода, и прогоняют их по учебной ИС. Сдают регрессионный набор и отчёт о прогоне.</t>
+          <t xml:space="preserve">Студенты проверяют учебную ИС целиком на соответствие сценариям пользователя. Сдают протокол системного прогона с найденными дефектами и оценкой готовности.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">регрессионный набор, зона риска, изменение, прогон, дымовой тест</t>
+          <t xml:space="preserve">сквозной сценарий, окружение, протокол, дефект, пользовательский путь</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 11. Системное тестирование</t>
+          <t xml:space="preserve">Лекция 12. Регрессионное тестирование</t>
         </is>
       </c>
       <c r="D22" s="6">
@@ -675,16 +675,16 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Системный тест проверяет готовую ИС в среде, близкой к рабочей: сценарии, данные, окружение и внешние системы. Разбирается, что именно проверяется на этом уровне.</t>
+          <t xml:space="preserve">Любое изменение может сломать то, что уже работало. Разбирается, как выбрать регрессионный набор, когда его прогонять и как не утонуть в бесконечных проверках.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">сквозной сценарий, окружение, внешняя система, приёмочный тест, готовность</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="60" customHeight="1">
+          <t xml:space="preserve">набор проверок, риск, автоматизация, дымовой прогон, частота</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">22</t>
@@ -692,12 +692,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 12. Регрессионное тестирование</t>
+          <t xml:space="preserve">Практика 6. Регрессия</t>
         </is>
       </c>
       <c r="D23" s="6">
@@ -705,102 +705,102 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любое изменение может сломать то, что уже работало. Разбирается, как выбрать регрессионный набор, когда его прогонять и как не утонуть в бесконечных проверках.</t>
+          <t xml:space="preserve">Студенты подбирают проверки, которые ловят поломки после изменения кода, и прогоняют их по учебной ИС. Сдают регрессионный набор и отчёт о прогоне.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">набор проверок, риск, автоматизация, дымовой прогон, частота</t>
+          <t xml:space="preserve">регрессионный набор, зона риска, изменение, прогон, дымовой тест</t>
         </is>
       </c>
     </row>
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Лекция 13. Тестирование API</t>
+        </is>
+      </c>
+      <c r="D24" s="6">
+        <v>2</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API проверяют без интерфейса: запрос, ответ, код состояния и тело. Разбираются контракт, негативные проверки и типовые дефекты обмена между системами.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">эндпоинт, код состояния, контракт, тело ответа, негативный тест, аутентификация</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 14. Postman</t>
+        </is>
+      </c>
+      <c r="D25" s="6">
+        <v>2</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postman хранит запросы, окружения и тесты в одном месте. Разбираются коллекции, переменные, окружения и запуск прогона из интерфейса.</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">коллекция, папка, переменная, окружение, прогон, тест-скрипт</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25-26</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика 7. API-тесты; Postman: коллекция</t>
         </is>
       </c>
-      <c r="D24" s="6">
+      <c r="D26" s="6">
         <v>4</v>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Студенты проверяют методы API учебной ИС в Postman и собирают запросы в коллекцию с переменными окружения. Сдают коллекцию и отчёт о проверке ответов.</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">запрос, ответ, переменная окружения, JSON, код состояния</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 13. Тестирование API</t>
-        </is>
-      </c>
-      <c r="D25" s="6">
-        <v>2</v>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">API проверяют без интерфейса: запрос, ответ, код состояния и тело. Разбираются контракт, негативные проверки и типовые дефекты обмена между системами.</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">эндпоинт, код состояния, контракт, тело ответа, негативный тест, аутентификация</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 8. Postman: тесты 200/500/JSON</t>
-        </is>
-      </c>
-      <c r="D26" s="6">
-        <v>2</v>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Студенты пишут в Postman проверки кода ответа и схемы JSON, включая обработку ошибки 500. Сдают коллекцию с тестами и отчёт о прогоне.</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">код ответа, схема JSON, тест-скрипт, прогон коллекции, ошибка сервера</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 14. Postman</t>
+          <t xml:space="preserve">Практика 8. Postman: тесты 200/500/JSON</t>
         </is>
       </c>
       <c r="D27" s="6">
@@ -825,16 +825,16 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postman хранит запросы, окружения и тесты в одном месте. Разбираются коллекции, переменные, окружения и запуск прогона из интерфейса.</t>
+          <t xml:space="preserve">Студенты пишут в Postman проверки кода ответа и схемы JSON, включая обработку ошибки 500. Сдают коллекцию с тестами и отчёт о прогоне.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">коллекция, папка, переменная, окружение, прогон, тест-скрипт</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="60" customHeight="1">
+          <t xml:space="preserve">код ответа, схема JSON, тест-скрипт, прогон коллекции, ошибка сервера</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">28</t>
@@ -842,55 +842,55 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Лекция 15. Автотесты</t>
+        </is>
+      </c>
+      <c r="D28" s="6">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Автотест окупается там, где проверку нужно повторять много раз. Разбираются пирамида тестов, выбор уровня автоматизации и цена поддержки набора.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">пирамида тестов, модульный тест, UI-тест, фикстура, поддержка, окупаемость</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика 9. Автотесты</t>
         </is>
       </c>
-      <c r="D28" s="6">
-        <v>2</v>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="D29" s="6">
+        <v>2</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Студенты переводят ручные проверки в автотесты на Python и запускают их на учебной ИС. Сдают набор тестов, который проходит на исправной сборке и падает на дефектной.</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">pytest, фикстура, утверждение, отчёт, запуск</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 15. Автотесты</t>
-        </is>
-      </c>
-      <c r="D29" s="6">
-        <v>2</v>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Автотест окупается там, где проверку нужно повторять много раз. Разбираются пирамида тестов, выбор уровня автоматизации и цена поддержки набора.</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">пирамида тестов, модульный тест, UI-тест, фикстура, поддержка, окупаемость</t>
         </is>
       </c>
     </row>
@@ -927,60 +927,60 @@
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-32</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 10. Нагрузка; Безопасность</t>
+          <t xml:space="preserve">Лекция 17. Безопасность</t>
         </is>
       </c>
       <c r="D31" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты задают нагрузку на учебную ИС и проверяют базовые риски безопасности: права доступа, ввод и хранение секретов. Сдают отчёт с метриками и найденными проблемами.</t>
+          <t xml:space="preserve">Проверки безопасности ищут, где система доверяет пользователю лишнее. Разбираются права доступа, валидация ввода, хранение секретов и типовые атаки на ИС.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">нагрузочный прогон, метрика, права доступа, валидация ввода, секрет</t>
+          <t xml:space="preserve">доступ, роль, валидация, инъекция, секрет, аутентификация</t>
         </is>
       </c>
     </row>
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">32-33</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 17. Безопасность</t>
+          <t xml:space="preserve">Практика 10. Нагрузка; Безопасность</t>
         </is>
       </c>
       <c r="D32" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Проверки безопасности ищут, где система доверяет пользователю лишнее. Разбираются права доступа, валидация ввода, хранение секретов и типовые атаки на ИС.</t>
+          <t xml:space="preserve">Студенты задают нагрузку на учебную ИС и проверяют базовые риски безопасности: права доступа, ввод и хранение секретов. Сдают отчёт с метриками и найденными проблемами.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">доступ, роль, валидация, инъекция, секрет, аутентификация</t>
+          <t xml:space="preserve">нагрузочный прогон, метрика, права доступа, валидация ввода, секрет</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 11. Юзабилити</t>
+          <t xml:space="preserve">Лекция 18. Юзабилити</t>
         </is>
       </c>
       <c r="D33" s="6">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проходят сценарии в интерфейсе учебной ИС и фиксируют затруднения пользователя. Сдают отчёт с найденными проблемами и предложениями по исправлению.</t>
+          <t xml:space="preserve">Удобство оценивают по тому, как быстро и без ошибок пользователь решает свою задачу. Разбираются эвристики, сценарии проверки и метрики удобства интерфейса.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">сценарий, эвристика, экран, затруднение, отчёт</t>
+          <t xml:space="preserve">эвристика, сценарий, метрика, обратная связь, доступность, экран</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 18. Юзабилити</t>
+          <t xml:space="preserve">Практика 11. Юзабилити</t>
         </is>
       </c>
       <c r="D34" s="6">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Удобство оценивают по тому, как быстро и без ошибок пользователь решает свою задачу. Разбираются эвристики, сценарии проверки и метрики удобства интерфейса.</t>
+          <t xml:space="preserve">Студенты проходят сценарии в интерфейсе учебной ИС и фиксируют затруднения пользователя. Сдают отчёт с найденными проблемами и предложениями по исправлению.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">эвристика, сценарий, метрика, обратная связь, доступность, экран</t>
+          <t xml:space="preserve">сценарий, эвристика, экран, затруднение, отчёт</t>
         </is>
       </c>
     </row>
@@ -1134,63 +1134,63 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
+    <row r="38" ht="45" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">40-41</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Практика 13. Отчёт; Тестовая документация</t>
+        </is>
+      </c>
+      <c r="D38" s="6">
+        <v>4</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Студенты собирают пакет тестовой документации по учебной ИС: план, наборы, отчёт и матрицу покрытия. Сдают документы, согласованные между собой.</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">матрица покрытия, шаблон, версия, согласованность, пакет документов</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Лекция 21. Организация тестирования</t>
         </is>
       </c>
-      <c r="D38" s="6">
-        <v>2</v>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="D39" s="6">
+        <v>2</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Тестирование встраивается в работу команды: роли, уровни, вход и выход из этапов. Разбираются стратегия, оценка трудозатрат и работа с рисками качества.</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">стратегия, роль, оценка, риск, процесс, метрика</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="45" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41-42</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 13. Отчёт; Тестовая документация</t>
-        </is>
-      </c>
-      <c r="D39" s="6">
-        <v>4</v>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Студенты собирают пакет тестовой документации по учебной ИС: план, наборы, отчёт и матрицу покрытия. Сдают документы, согласованные между собой.</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">матрица покрытия, шаблон, версия, согласованность, пакет документов</t>
         </is>
       </c>
     </row>

--- a/courses/3/is-testing/dist/Учебный_план_Тестирование_информационных_систем.xlsx
+++ b/courses/3/is-testing/dist/Учебный_план_Тестирование_информационных_систем.xlsx
@@ -315,7 +315,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты составляют тест-план учебной ИС и разбивают поля ввода на классы эквивалентности. Сдают тест-план и таблицу классов с обоснованием выбранных значений.</t>
+          <t xml:space="preserve">Вы составляете тест-план учебной ИС и разбиваете поля ввода на классы эквивалентности. Сдаёте тест-план и таблицу классов с обоснованием выбранных значений.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -405,7 +405,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проверяют форму ввода граничными значениями и оформляют найденные проверки как тест-кейсы. Сдают набор тест-кейсов с шагами, данными и ожидаемым результатом.</t>
+          <t xml:space="preserve">Вы проверяете форму ввода граничными значениями и оформляете найденные проверки как тест-кейсы. Сдаёте набор тест-кейсов с шагами, данными и ожидаемым результатом.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проверяют требования учебной ИС по чек-листу и фиксируют противоречия, пробелы и непроверяемые формулировки. Сдают чек-лист и список замечаний с вопросами к заказчику.</t>
+          <t xml:space="preserve">Вы проверяете требования учебной ИС по чек-листу и фиксируете противоречия, пробелы и непроверяемые формулировки. Сдаёте чек-лист и список замечаний с вопросами к заказчику.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">17-18</t>
@@ -585,7 +585,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проверяют функции учебной ИС по требованиям и стыки между модулями. Сдают набор функциональных и интеграционных тестов с результатами прогона.</t>
+          <t xml:space="preserve">Вы проверяете функции учебной ИС по требованиям и стыки между модулями. Сдаёте набор функциональных и интеграционных тестов с результатами прогона.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проверяют учебную ИС целиком на соответствие сценариям пользователя. Сдают протокол системного прогона с найденными дефектами и оценкой готовности.</t>
+          <t xml:space="preserve">Вы проверяете учебную ИС целиком на соответствие сценариям пользователя. Сдаёте протокол системного прогона с найденными дефектами и оценкой готовности.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты подбирают проверки, которые ловят поломки после изменения кода, и прогоняют их по учебной ИС. Сдают регрессионный набор и отчёт о прогоне.</t>
+          <t xml:space="preserve">Вы подбираете проверки, которые ловят поломки после изменения кода, и прогоняете их по учебной ИС. Сдаёте регрессионный набор и отчёт о прогоне.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -774,7 +774,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">25-26</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проверяют методы API учебной ИС в Postman и собирают запросы в коллекцию с переменными окружения. Сдают коллекцию и отчёт о проверке ответов.</t>
+          <t xml:space="preserve">Вы проверяете методы API учебной ИС в Postman и собираете запросы в коллекцию с переменными окружения. Сдаёте коллекцию и отчёт о проверке ответов.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты пишут в Postman проверки кода ответа и схемы JSON, включая обработку ошибки 500. Сдают коллекцию с тестами и отчёт о прогоне.</t>
+          <t xml:space="preserve">Вы пишете в Postman проверки кода ответа и схемы JSON, включая обработку ошибки 500. Сдаёте коллекцию с тестами и отчёт о прогоне.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты переводят ручные проверки в автотесты на Python и запускают их на учебной ИС. Сдают набор тестов, который проходит на исправной сборке и падает на дефектной.</t>
+          <t xml:space="preserve">Вы переводите ручные проверки в автотесты на Python и запускаете их на учебной ИС. Сдаёте набор тестов, который проходит на исправной сборке и падает на дефектной.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты задают нагрузку на учебную ИС и проверяют базовые риски безопасности: права доступа, ввод и хранение секретов. Сдают отчёт с метриками и найденными проблемами.</t>
+          <t xml:space="preserve">Вы задаёте нагрузку на учебную ИС и проверяете базовые риски безопасности: права доступа, ввод и хранение секретов. Сдаёте отчёт с метриками и найденными проблемами.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проходят сценарии в интерфейсе учебной ИС и фиксируют затруднения пользователя. Сдают отчёт с найденными проблемами и предложениями по исправлению.</t>
+          <t xml:space="preserve">Вы проходите сценарии в интерфейсе учебной ИС и фиксируете затруднения пользователя. Сдаёте отчёт с найденными проблемами и предложениями по исправлению.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты воспроизводят дефекты учебной ИС, оформляют баг-репорты и проводят их по статусам в трекере. Сдают набор баг-репортов и выгрузку истории статусов.</t>
+          <t xml:space="preserve">Вы воспроизводите дефекты учебной ИС, оформляете баг-репорты и проводите их по статусам в трекере. Сдаёте набор баг-репортов и выгрузку истории статусов.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты собирают пакет тестовой документации по учебной ИС: план, наборы, отчёт и матрицу покрытия. Сдают документы, согласованные между собой.</t>
+          <t xml:space="preserve">Вы собираете пакет тестовой документации по учебной ИС: план, наборы, отчёт и матрицу покрытия. Сдаёте документы, согласованные между собой.</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
@@ -1194,7 +1194,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
+    <row r="40" ht="45" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">43-44</t>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проверяют сохранение данных в БД и работу интерфейса учебной ИС. Сдают SQL-запросы проверки данных и набор тестов интерфейса с результатами.</t>
+          <t xml:space="preserve">Вы проверяете сохранение данных в БД и работу интерфейса учебной ИС. Сдаёте SQL-запросы проверки данных и набор тестов интерфейса с результатами.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проверяют обмен учебной ИС с внешним сервисом и поведение при сбое. Сдают набор тестов интеграции и отчёт об обработке ошибок.</t>
+          <t xml:space="preserve">Вы проверяете обмен учебной ИС с внешним сервисом и поведение при сбое. Сдаёте набор тестов интеграции и отчёт об обработке ошибок.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты проводят цикл тестирования небольшой ИС от плана до отчёта. Сдают пакет документов и защищают принятые решения по объёму проверок.</t>
+          <t xml:space="preserve">Вы проводите цикл тестирования небольшой ИС от плана до отчёта. Сдаёте пакет документов и защищаете принятые решения по объёму проверок.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты сводят результаты проверок в итоговый отчёт с метриками и выводом о готовности. Сдают отчёт и презентацию для защиты.</t>
+          <t xml:space="preserve">Вы сводите результаты проверок в итоговый отчёт с метриками и выводом о готовности. Сдаёте отчёт и презентацию для защиты.</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Студенты защищают результаты тестирования учебной ИС: объём проверок, найденные дефекты и вывод о качестве. Сдают доклад и отвечают на вопросы по решениям.</t>
+          <t xml:space="preserve">Вы защищаете результаты тестирования учебной ИС: объём проверок, найденные дефекты и вывод о качестве. Сдаёте доклад и отвечаете на вопросы по решениям.</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">

--- a/courses/3/is-testing/dist/Учебный_план_Тестирование_информационных_систем.xlsx
+++ b/courses/3/is-testing/dist/Учебный_план_Тестирование_информационных_систем.xlsx
@@ -109,7 +109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -307,7 +307,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Тест-план; Классы эквивалентности</t>
+          <t xml:space="preserve">Практика 1. План тестирования учебной системы</t>
         </is>
       </c>
       <c r="D10" s="6">
@@ -397,7 +397,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 2. Граничные значения; Тест-кейсы</t>
+          <t xml:space="preserve">Практика 2. Набор проверок для формы приёмки</t>
         </is>
       </c>
       <c r="D13" s="6">
@@ -487,7 +487,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 3. Чек-лист; Тестирование требований</t>
+          <t xml:space="preserve">Практика 3. Проверка требований к складу</t>
         </is>
       </c>
       <c r="D16" s="6">
@@ -577,7 +577,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 4. Функциональные тесты; Интеграционные тесты</t>
+          <t xml:space="preserve">Практика 4. Сквозные сценарии приёмки и отгрузки</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -637,7 +637,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 5. Системные тесты</t>
+          <t xml:space="preserve">Практика 5. Проверка системы целиком на стенде</t>
         </is>
       </c>
       <c r="D21" s="6">
@@ -697,7 +697,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 6. Регрессия</t>
+          <t xml:space="preserve">Практика 6. Набор проверок после обновления</t>
         </is>
       </c>
       <c r="D23" s="6">
@@ -787,7 +787,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 7. API-тесты; Postman: коллекция</t>
+          <t xml:space="preserve">Практика 7. Коллекция запросов к API склада</t>
         </is>
       </c>
       <c r="D26" s="6">
@@ -817,7 +817,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 8. Postman: тесты 200/500/JSON</t>
+          <t xml:space="preserve">Практика 8. Проверки ответов API в Postman</t>
         </is>
       </c>
       <c r="D27" s="6">
@@ -877,7 +877,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 9. Автотесты</t>
+          <t xml:space="preserve">Практика 9. Первый набор автотестов на pytest</t>
         </is>
       </c>
       <c r="D29" s="6">
@@ -967,7 +967,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 10. Нагрузка; Безопасность</t>
+          <t xml:space="preserve">Практика 10. Проверка нагрузки и доступа</t>
         </is>
       </c>
       <c r="D32" s="6">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 11. Юзабилити</t>
+          <t xml:space="preserve">Практика 11. Оценка удобства интерфейса склада</t>
         </is>
       </c>
       <c r="D34" s="6">
@@ -1077,7 +1077,7 @@
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">37-38</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -1087,11 +1087,11 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 12. Баг-репорт; Bug tracking</t>
+          <t xml:space="preserve">Практика 12. Журнал дефектов учебной системы</t>
         </is>
       </c>
       <c r="D36" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     <row r="37" ht="45" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="38" ht="45" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">40-41</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -1147,11 +1147,11 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 13. Отчёт; Тестовая документация</t>
+          <t xml:space="preserve">Практика 13. Итоговая документация тестирования</t>
         </is>
       </c>
       <c r="D38" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
     <row r="39" ht="60" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 21. Организация тестирования</t>
+          <t xml:space="preserve">Лекция 21. Тестирование баз данных</t>
         </is>
       </c>
       <c r="D39" s="6">
@@ -1185,49 +1185,49 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тестирование встраивается в работу команды: роли, уровни, вход и выход из этапов. Разбираются стратегия, оценка трудозатрат и работа с рисками качества.</t>
+          <t xml:space="preserve">Проверка схемы, ограничений, транзакций и самих данных: как найти дубликат, потерянную связь и неверный тип. Вы построите набор запросов, которые проверяют базу склада и объясняют результат.</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">стратегия, роль, оценка, риск, процесс, метрика</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="45" customHeight="1">
+          <t xml:space="preserve">схема, ограничение, дубликат, потерянная связь, транзакция, откат</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">43-44</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 14. Тестирование БД; Тестирование интерфейса</t>
+          <t xml:space="preserve">Лекция 22. Тестирование интерфейса</t>
         </is>
       </c>
       <c r="D40" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вы проверяете сохранение данных в БД и работу интерфейса учебной ИС. Сдаёте SQL-запросы проверки данных и набор тестов интерфейса с результатами.</t>
+          <t xml:space="preserve">Проверка экранов склада: обязательные поля, состояния кнопок, сообщения об ошибках и работа с клавиатуры. Вы составите набор проверок интерфейса и найдёте дефекты, которые не видны в API.</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">целостность данных, SQL-проверка, валидация поля, расхождение, транзакция</t>
+          <t xml:space="preserve">экран, обязательное поле, сообщение об ошибке, состояние элемента, клавиатура, доступность</t>
         </is>
       </c>
     </row>
     <row r="41" ht="45" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">42-43</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -1237,37 +1237,37 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 15. Тестирование интеграций</t>
+          <t xml:space="preserve">Практика 14. Проверка данных и интерфейса</t>
         </is>
       </c>
       <c r="D41" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вы проверяете обмен учебной ИС с внешним сервисом и поведение при сбое. Сдаёте набор тестов интеграции и отчёт об обработке ошибок.</t>
+          <t xml:space="preserve">Вы проверяете сохранение данных в БД и работу интерфейса учебной ИС. Сдаёте SQL-запросы проверки данных и набор тестов интерфейса с результатами.</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">внешний сервис, таймаут, повтор, идемпотентность, очередь</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
+          <t xml:space="preserve">целостность данных, SQL-проверка, валидация поля, расхождение, транзакция</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">46</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 16. Мини-проект</t>
+          <t xml:space="preserve">Лекция 23. Организация тестирования</t>
         </is>
       </c>
       <c r="D42" s="6">
@@ -1275,112 +1275,172 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вы проводите цикл тестирования небольшой ИС от плана до отчёта. Сдаёте пакет документов и защищаете принятые решения по объёму проверок.</t>
+          <t xml:space="preserve">Тестирование встраивается в работу команды: роли, уровни, вход и выход из этапов. Разбираются стратегия, оценка трудозатрат и работа с рисками качества.</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">цикл тестирования, план, дефект, отчёт, защита</t>
+          <t xml:space="preserve">стратегия, роль, оценка, риск, процесс, метрика</t>
         </is>
       </c>
     </row>
     <row r="43" ht="45" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">45</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика 15. Обмен данными между складом и бухгалтерией</t>
+        </is>
+      </c>
+      <c r="D43" s="6">
+        <v>2</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вы проверяете обмен учебной ИС с внешним сервисом и поведение при сбое. Сдаёте набор тестов интеграции и отчёт об обработке ошибок.</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">внешний сервис, таймаут, повтор, идемпотентность, очередь</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="45" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика 16. Мини-проект: тестирование модуля</t>
+        </is>
+      </c>
+      <c r="D44" s="6">
+        <v>2</v>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вы проводите цикл тестирования небольшой ИС от плана до отчёта. Сдаёте пакет документов и защищаете принятые решения по объёму проверок.</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">цикл тестирования, план, дефект, отчёт, защита</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">47</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 17. Итоговый отчёт</t>
-        </is>
-      </c>
-      <c r="D43" s="6">
-        <v>2</v>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика 17. Сводный отчёт по проекту</t>
+        </is>
+      </c>
+      <c r="D45" s="6">
+        <v>2</v>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Вы сводите результаты проверок в итоговый отчёт с метриками и выводом о готовности. Сдаёте отчёт и презентацию для защиты.</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">метрика, готовность, презентация, вывод, сводка</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">48</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 18. Защита</t>
-        </is>
-      </c>
-      <c r="D44" s="6">
-        <v>2</v>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика 18. Защита проекта</t>
+        </is>
+      </c>
+      <c r="D46" s="6">
+        <v>2</v>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Вы защищаете результаты тестирования учебной ИС: объём проверок, найденные дефекты и вывод о качестве. Сдаёте доклад и отвечаете на вопросы по решениям.</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">доклад, обоснование, вопросы, качество, вывод</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Итого</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="D45" s="6">
+      <c r="D47" s="6">
         <v>96</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39 позиций</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41 позиция</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F44"/>
+  <autoFilter ref="A5:F46"/>
   <mergeCells count="4">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A47:C47"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
